--- a/Docs/Product Backlog.xlsx
+++ b/Docs/Product Backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0d25a1f11c8555b/Desktop/SpaceLandMapper Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{D62DBAEE-B1C0-4FE6-A20A-774BF33019AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01754342-DFE3-417F-90DF-A470CEF6E624}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{D62DBAEE-B1C0-4FE6-A20A-774BF33019AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C703554-82E0-409D-A82F-10ACB0EA04B0}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
